--- a/data/metadata_raw/electricity_production.xlsx
+++ b/data/metadata_raw/electricity_production.xlsx
@@ -515,7 +515,7 @@
     <t>2022-06-28</t>
   </si>
   <si>
-    <t>2024-08-29</t>
+    <t>2025-09-03</t>
   </si>
   <si>
     <t>1.02.02.0004</t>
